--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/96.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/96.xlsx
@@ -426,13 +426,13 @@
         <v>-10.87084596165289</v>
       </c>
       <c r="E2">
-        <v>-11.34846209483169</v>
+        <v>-7.444297099280795</v>
       </c>
       <c r="F2">
-        <v>-3.346987988665007</v>
+        <v>-3.762431636884418</v>
       </c>
       <c r="G2">
-        <v>-7.189417827885044</v>
+        <v>-5.457388934294997</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.60443729829684</v>
       </c>
       <c r="E3">
-        <v>-11.40285812461183</v>
+        <v>-8.768463655389677</v>
       </c>
       <c r="F3">
-        <v>-3.191689809825169</v>
+        <v>-3.253449569908289</v>
       </c>
       <c r="G3">
-        <v>-6.922273893401293</v>
+        <v>-5.591846831357922</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.31934538886099</v>
       </c>
       <c r="E4">
-        <v>-12.55966586681924</v>
+        <v>-8.461011969586913</v>
       </c>
       <c r="F4">
-        <v>-3.172658068745851</v>
+        <v>-3.293088606867051</v>
       </c>
       <c r="G4">
-        <v>-7.391777323899118</v>
+        <v>-6.032334419605578</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.03853941956474</v>
       </c>
       <c r="E5">
-        <v>-13.59725700230072</v>
+        <v>-10.08720057116336</v>
       </c>
       <c r="F5">
-        <v>-3.006205922827318</v>
+        <v>-2.739459193614835</v>
       </c>
       <c r="G5">
-        <v>-6.631597037893204</v>
+        <v>-5.729960009238069</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.738874155043675</v>
       </c>
       <c r="E6">
-        <v>-13.14339069488195</v>
+        <v>-10.19859197480404</v>
       </c>
       <c r="F6">
-        <v>-3.07834346973271</v>
+        <v>-3.50105107170727</v>
       </c>
       <c r="G6">
-        <v>-6.838192590940522</v>
+        <v>-5.090463052188531</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.40778367336835</v>
       </c>
       <c r="E7">
-        <v>-14.08648616324538</v>
+        <v>-11.69161626971093</v>
       </c>
       <c r="F7">
-        <v>-2.848980961408569</v>
+        <v>-2.856133913931743</v>
       </c>
       <c r="G7">
-        <v>-6.433437505475219</v>
+        <v>-5.730222506962825</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.015100538861851</v>
       </c>
       <c r="E8">
-        <v>-14.21565182736616</v>
+        <v>-11.584798624818</v>
       </c>
       <c r="F8">
-        <v>-2.748827200573095</v>
+        <v>-2.966945449771635</v>
       </c>
       <c r="G8">
-        <v>-6.283902395346645</v>
+        <v>-5.813175069207147</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.556741390511601</v>
       </c>
       <c r="E9">
-        <v>-15.62347741229274</v>
+        <v>-13.04359671317492</v>
       </c>
       <c r="F9">
-        <v>-2.961334917352474</v>
+        <v>-3.241997390564586</v>
       </c>
       <c r="G9">
-        <v>-6.173220229703456</v>
+        <v>-5.367437526464379</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.027649120613807</v>
       </c>
       <c r="E10">
-        <v>-15.57744094553076</v>
+        <v>-13.11548623804669</v>
       </c>
       <c r="F10">
-        <v>-2.723399634776761</v>
+        <v>-2.918669025903883</v>
       </c>
       <c r="G10">
-        <v>-5.411425582690295</v>
+        <v>-4.545153560002855</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.434116072118992</v>
       </c>
       <c r="E11">
-        <v>-16.83828584959039</v>
+        <v>-14.76628256738082</v>
       </c>
       <c r="F11">
-        <v>-2.81908683857634</v>
+        <v>-2.554638000539224</v>
       </c>
       <c r="G11">
-        <v>-5.413751968775942</v>
+        <v>-4.98133290434296</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.791263895488607</v>
       </c>
       <c r="E12">
-        <v>-17.04933538071787</v>
+        <v>-13.94885678120426</v>
       </c>
       <c r="F12">
-        <v>-2.545096864793779</v>
+        <v>-2.318438976039778</v>
       </c>
       <c r="G12">
-        <v>-4.006852757068152</v>
+        <v>-4.414423130631459</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.105050955614712</v>
       </c>
       <c r="E13">
-        <v>-17.91263913706614</v>
+        <v>-15.04999599243538</v>
       </c>
       <c r="F13">
-        <v>-2.668568339650656</v>
+        <v>-2.545803462188367</v>
       </c>
       <c r="G13">
-        <v>-3.684131491810527</v>
+        <v>-3.297790621736827</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.398278501926278</v>
       </c>
       <c r="E14">
-        <v>-18.44274230440403</v>
+        <v>-15.74140340392649</v>
       </c>
       <c r="F14">
-        <v>-3.026999601372391</v>
+        <v>-2.578645744607159</v>
       </c>
       <c r="G14">
-        <v>-3.606445290169114</v>
+        <v>-2.199329517838401</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.68847793716329</v>
       </c>
       <c r="E15">
-        <v>-19.17957031019207</v>
+        <v>-16.1971309141624</v>
       </c>
       <c r="F15">
-        <v>-2.470908280199055</v>
+        <v>-2.80003107484234</v>
       </c>
       <c r="G15">
-        <v>-2.389837241579762</v>
+        <v>-2.789631120047184</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.000503230827055</v>
       </c>
       <c r="E16">
-        <v>-19.83601790234397</v>
+        <v>-17.03938179484901</v>
       </c>
       <c r="F16">
-        <v>-2.439493274815287</v>
+        <v>-2.614046853933198</v>
       </c>
       <c r="G16">
-        <v>-1.809891174612586</v>
+        <v>-0.6494904513365219</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.365389461579928</v>
       </c>
       <c r="E17">
-        <v>-20.02390428892221</v>
+        <v>-17.7810190400332</v>
       </c>
       <c r="F17">
-        <v>-2.537545467549859</v>
+        <v>-1.963032083705664</v>
       </c>
       <c r="G17">
-        <v>-1.126288037360993</v>
+        <v>0.09055297795907982</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.802203100707823</v>
       </c>
       <c r="E18">
-        <v>-20.77979717028255</v>
+        <v>-19.27122662410732</v>
       </c>
       <c r="F18">
-        <v>-2.330574558490791</v>
+        <v>-2.130970320744819</v>
       </c>
       <c r="G18">
-        <v>-0.8629043827843657</v>
+        <v>0.04958364556785309</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.334526366367859</v>
       </c>
       <c r="E19">
-        <v>-21.65397832119724</v>
+        <v>-20.15357714213185</v>
       </c>
       <c r="F19">
-        <v>-2.027672905615721</v>
+        <v>-1.806188171292203</v>
       </c>
       <c r="G19">
-        <v>0.3338850875859405</v>
+        <v>0.6687829660506655</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.966610969131244</v>
       </c>
       <c r="E20">
-        <v>-23.00333677821079</v>
+        <v>-19.61746921825979</v>
       </c>
       <c r="F20">
-        <v>-1.748692846598695</v>
+        <v>-1.459108856458432</v>
       </c>
       <c r="G20">
-        <v>1.015949331926154</v>
+        <v>1.158603720444572</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.696035396627217</v>
       </c>
       <c r="E21">
-        <v>-24.15881314905995</v>
+        <v>-20.86070741537759</v>
       </c>
       <c r="F21">
-        <v>-1.5419505669428</v>
+        <v>-1.567937280736023</v>
       </c>
       <c r="G21">
-        <v>0.8604948981043418</v>
+        <v>0.4761818229543795</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.513090536012445</v>
       </c>
       <c r="E22">
-        <v>-24.20143514642014</v>
+        <v>-22.5260718455944</v>
       </c>
       <c r="F22">
-        <v>-1.561202653751263</v>
+        <v>-1.149600145178634</v>
       </c>
       <c r="G22">
-        <v>0.5048039186174157</v>
+        <v>0.9868448966938794</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.396753799479719</v>
       </c>
       <c r="E23">
-        <v>-25.13005308338104</v>
+        <v>-23.10958836385276</v>
       </c>
       <c r="F23">
-        <v>-1.361465877220844</v>
+        <v>-0.9021046744072113</v>
       </c>
       <c r="G23">
-        <v>0.5946470461365715</v>
+        <v>1.096408165785298</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.330699543712076</v>
       </c>
       <c r="E24">
-        <v>-24.70711172496066</v>
+        <v>-23.68235428481692</v>
       </c>
       <c r="F24">
-        <v>-1.305792960813494</v>
+        <v>-0.7917611661499004</v>
       </c>
       <c r="G24">
-        <v>0.5885833486947176</v>
+        <v>1.195737304832808</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.291570105846744</v>
       </c>
       <c r="E25">
-        <v>-25.94985631841163</v>
+        <v>-22.26054477215465</v>
       </c>
       <c r="F25">
-        <v>-0.9206410517796559</v>
+        <v>-0.7097055763307898</v>
       </c>
       <c r="G25">
-        <v>0.7245079517947151</v>
+        <v>0.4122964391919909</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.26100817867066</v>
       </c>
       <c r="E26">
-        <v>-26.05752984489201</v>
+        <v>-23.80283433579099</v>
       </c>
       <c r="F26">
-        <v>-1.16821107561733</v>
+        <v>-0.5967701064701192</v>
       </c>
       <c r="G26">
-        <v>0.03788280948687324</v>
+        <v>1.276901601327233</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.224125439547134</v>
       </c>
       <c r="E27">
-        <v>-25.82885549292667</v>
+        <v>-23.3126451383567</v>
       </c>
       <c r="F27">
-        <v>-1.226648254047821</v>
+        <v>-0.9773543976449213</v>
       </c>
       <c r="G27">
-        <v>-0.03963276863344872</v>
+        <v>-0.1692935197764661</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.168352419464759</v>
       </c>
       <c r="E28">
-        <v>-25.91904910973744</v>
+        <v>-24.23820182688841</v>
       </c>
       <c r="F28">
-        <v>-1.059242657248666</v>
+        <v>-0.3617738714395387</v>
       </c>
       <c r="G28">
-        <v>-0.6134363888413434</v>
+        <v>0.3558594283695418</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.089271444110022</v>
       </c>
       <c r="E29">
-        <v>-25.93897439537119</v>
+        <v>-23.00321450941259</v>
       </c>
       <c r="F29">
-        <v>-0.9604300232383246</v>
+        <v>-0.6927000219187187</v>
       </c>
       <c r="G29">
-        <v>-0.9745118529073182</v>
+        <v>-1.498893713986857</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.983241825857498</v>
       </c>
       <c r="E30">
-        <v>-25.91574785218585</v>
+        <v>-22.19238218139119</v>
       </c>
       <c r="F30">
-        <v>-0.8185489112216309</v>
+        <v>-0.5473107739511691</v>
       </c>
       <c r="G30">
-        <v>-1.331092043436854</v>
+        <v>-0.9512742418233308</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.8514381752060798</v>
       </c>
       <c r="E31">
-        <v>-26.06968426912859</v>
+        <v>-22.5433117461416</v>
       </c>
       <c r="F31">
-        <v>-1.049815836204808</v>
+        <v>-0.9319225874383824</v>
       </c>
       <c r="G31">
-        <v>-1.150660951104548</v>
+        <v>-0.3254632598982374</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.6981997741194954</v>
       </c>
       <c r="E32">
-        <v>-26.00049824323941</v>
+        <v>-23.18068540577319</v>
       </c>
       <c r="F32">
-        <v>-0.9091863873337444</v>
+        <v>-0.5123992297601839</v>
       </c>
       <c r="G32">
-        <v>-1.604332487578053</v>
+        <v>-0.5709248823171776</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.5312365575542873</v>
       </c>
       <c r="E33">
-        <v>-24.91055794822926</v>
+        <v>-22.32954060213551</v>
       </c>
       <c r="F33">
-        <v>-1.254782924516504</v>
+        <v>-0.1816139017394797</v>
       </c>
       <c r="G33">
-        <v>-1.806567297172869</v>
+        <v>-1.687216144169627</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.362269246537686</v>
       </c>
       <c r="E34">
-        <v>-25.41958559753545</v>
+        <v>-21.19023088349374</v>
       </c>
       <c r="F34">
-        <v>-0.888988304951284</v>
+        <v>-0.280412453503974</v>
       </c>
       <c r="G34">
-        <v>-2.083837081389066</v>
+        <v>-1.80549433772293</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.2005459809956892</v>
       </c>
       <c r="E35">
-        <v>-23.88878477245657</v>
+        <v>-20.79129496578802</v>
       </c>
       <c r="F35">
-        <v>-0.950314000515337</v>
+        <v>-0.7160417585948032</v>
       </c>
       <c r="G35">
-        <v>-2.407565681665441</v>
+        <v>-2.747982574793152</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.05704824744173451</v>
       </c>
       <c r="E36">
-        <v>-22.91432509311602</v>
+        <v>-21.49746520254414</v>
       </c>
       <c r="F36">
-        <v>-0.8179864497551299</v>
+        <v>-0.1270915876546191</v>
       </c>
       <c r="G36">
-        <v>-2.407224434623259</v>
+        <v>-1.649098193313557</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.05840803976497346</v>
       </c>
       <c r="E37">
-        <v>-23.30463879631114</v>
+        <v>-21.12705414261274</v>
       </c>
       <c r="F37">
-        <v>-0.8260928531589259</v>
+        <v>-0.3280245267146812</v>
       </c>
       <c r="G37">
-        <v>-2.692385556689921</v>
+        <v>-2.043015403968014</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.1344433777081768</v>
       </c>
       <c r="E38">
-        <v>-23.361819837606</v>
+        <v>-19.93523676785203</v>
       </c>
       <c r="F38">
-        <v>-0.5536055378450425</v>
+        <v>-0.2048388386117695</v>
       </c>
       <c r="G38">
-        <v>-2.715265514623929</v>
+        <v>-2.24932549073966</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.1584196508877593</v>
       </c>
       <c r="E39">
-        <v>-22.4424716869388</v>
+        <v>-19.62067537785722</v>
       </c>
       <c r="F39">
-        <v>-0.7841294172679085</v>
+        <v>-0.1911475821782993</v>
       </c>
       <c r="G39">
-        <v>-2.335168809177853</v>
+        <v>-2.208208503378259</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.1201934093522471</v>
       </c>
       <c r="E40">
-        <v>-22.21526908902596</v>
+        <v>-18.58518998278931</v>
       </c>
       <c r="F40">
-        <v>-0.682159046718095</v>
+        <v>-0.2484175909382459</v>
       </c>
       <c r="G40">
-        <v>-1.838214679113713</v>
+        <v>-1.835409234680388</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.009748361561610382</v>
       </c>
       <c r="E41">
-        <v>-21.05104370639399</v>
+        <v>-17.76517843795437</v>
       </c>
       <c r="F41">
-        <v>-0.5955938247581439</v>
+        <v>-0.3868965980316421</v>
       </c>
       <c r="G41">
-        <v>-1.925176894103676</v>
+        <v>-2.239685261798012</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.1747809026996543</v>
       </c>
       <c r="E42">
-        <v>-22.03773479402925</v>
+        <v>-18.07628460228132</v>
       </c>
       <c r="F42">
-        <v>-0.4281360408126126</v>
+        <v>-0.09935204843707206</v>
       </c>
       <c r="G42">
-        <v>-2.299387088072108</v>
+        <v>-2.015659859826924</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.4319196926127882</v>
       </c>
       <c r="E43">
-        <v>-20.45039597096461</v>
+        <v>-18.03418337943201</v>
       </c>
       <c r="F43">
-        <v>-0.3786245211472862</v>
+        <v>-0.1528049402049186</v>
       </c>
       <c r="G43">
-        <v>-1.885730048516032</v>
+        <v>-2.539490475684476</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.7518128066126494</v>
       </c>
       <c r="E44">
-        <v>-20.22522665788121</v>
+        <v>-16.60965225389113</v>
       </c>
       <c r="F44">
-        <v>-0.2422338282763476</v>
+        <v>-0.242248738889598</v>
       </c>
       <c r="G44">
-        <v>-1.752768388484213</v>
+        <v>-1.488840051128718</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.118079979103478</v>
       </c>
       <c r="E45">
-        <v>-19.86036297860921</v>
+        <v>-16.79100858095031</v>
       </c>
       <c r="F45">
-        <v>-0.4447514341779651</v>
+        <v>-0.04140195003942704</v>
       </c>
       <c r="G45">
-        <v>-2.05214376234639</v>
+        <v>-1.453265046981218</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.512870607428544</v>
       </c>
       <c r="E46">
-        <v>-19.52365282224288</v>
+        <v>-15.45179390571394</v>
       </c>
       <c r="F46">
-        <v>-0.174155281644673</v>
+        <v>-0.07396921448048961</v>
       </c>
       <c r="G46">
-        <v>-1.963898589726683</v>
+        <v>-1.176956660681938</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.912781955859863</v>
       </c>
       <c r="E47">
-        <v>-19.14282174361983</v>
+        <v>-15.19188666851771</v>
       </c>
       <c r="F47">
-        <v>-0.3039032963125624</v>
+        <v>0.4218633483435993</v>
       </c>
       <c r="G47">
-        <v>-1.621463745339914</v>
+        <v>-1.48268119826164</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.300246914212346</v>
       </c>
       <c r="E48">
-        <v>-18.23273885077232</v>
+        <v>-15.05480976030553</v>
       </c>
       <c r="F48">
-        <v>-0.4473483659857416</v>
+        <v>-0.3633370007286213</v>
       </c>
       <c r="G48">
-        <v>-2.337363946401121</v>
+        <v>-1.848990210714929</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.658435104658718</v>
       </c>
       <c r="E49">
-        <v>-19.06667545318085</v>
+        <v>-15.79587641776475</v>
       </c>
       <c r="F49">
-        <v>-0.2338540636296278</v>
+        <v>0.1469389761306797</v>
       </c>
       <c r="G49">
-        <v>-1.907057988652423</v>
+        <v>-0.4905316728892227</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.976633007739518</v>
       </c>
       <c r="E50">
-        <v>-17.92192703725587</v>
+        <v>-14.69324733858511</v>
       </c>
       <c r="F50">
-        <v>-0.2016405120695606</v>
+        <v>-0.3241229162474955</v>
       </c>
       <c r="G50">
-        <v>-1.835678294848262</v>
+        <v>-1.510286115241249</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.250970526872281</v>
       </c>
       <c r="E51">
-        <v>-17.60486140113482</v>
+        <v>-13.05119549255979</v>
       </c>
       <c r="F51">
-        <v>-0.06302151088509134</v>
+        <v>0.1634938986756279</v>
       </c>
       <c r="G51">
-        <v>-2.25068719768683</v>
+        <v>-1.111601289660918</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.479167738271062</v>
       </c>
       <c r="E52">
-        <v>-17.21833350221012</v>
+        <v>-14.28648168932013</v>
       </c>
       <c r="F52">
-        <v>0.06652686723872335</v>
+        <v>-0.006101073169126111</v>
       </c>
       <c r="G52">
-        <v>-1.650338495063028</v>
+        <v>-0.6963364515407141</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.667731490992247</v>
       </c>
       <c r="E53">
-        <v>-15.41481891544131</v>
+        <v>-13.43594370119948</v>
       </c>
       <c r="F53">
-        <v>-0.406108923204771</v>
+        <v>-0.1746092269814071</v>
       </c>
       <c r="G53">
-        <v>-2.373733006166007</v>
+        <v>-2.636552290634409</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.82189851479946</v>
       </c>
       <c r="E54">
-        <v>-15.49211996675225</v>
+        <v>-12.46289237727532</v>
       </c>
       <c r="F54">
-        <v>-0.3837198090419059</v>
+        <v>0.02074134415118907</v>
       </c>
       <c r="G54">
-        <v>-2.694314914966874</v>
+        <v>-2.363334815044126</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.948753343936524</v>
       </c>
       <c r="E55">
-        <v>-16.32895932099969</v>
+        <v>-12.68170371285195</v>
       </c>
       <c r="F55">
-        <v>-0.05189239482847998</v>
+        <v>0.2088271331612336</v>
       </c>
       <c r="G55">
-        <v>-2.544304027712181</v>
+        <v>-2.086498152073776</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.056903445723749</v>
       </c>
       <c r="E56">
-        <v>-15.07305498208243</v>
+        <v>-11.07625099375662</v>
       </c>
       <c r="F56">
-        <v>-0.05905031755607051</v>
+        <v>-0.02292190165037287</v>
       </c>
       <c r="G56">
-        <v>-2.781070412998593</v>
+        <v>-2.102687699248076</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.149746438699286</v>
       </c>
       <c r="E57">
-        <v>-14.70907888371593</v>
+        <v>-11.99351604638029</v>
       </c>
       <c r="F57">
-        <v>0.02366299598086292</v>
+        <v>-0.1902968488556242</v>
       </c>
       <c r="G57">
-        <v>-3.167782061108509</v>
+        <v>-2.722188892114357</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.23449278978992</v>
       </c>
       <c r="E58">
-        <v>-13.74104510899227</v>
+        <v>-11.35764584011925</v>
       </c>
       <c r="F58">
-        <v>-0.0714692016588407</v>
+        <v>0.247448106581955</v>
       </c>
       <c r="G58">
-        <v>-3.291024742881253</v>
+        <v>-3.091008039060621</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.312069966165176</v>
       </c>
       <c r="E59">
-        <v>-13.46663316954947</v>
+        <v>-10.1719419052689</v>
       </c>
       <c r="F59">
-        <v>0.08375276737993906</v>
+        <v>0.2914675503667207</v>
       </c>
       <c r="G59">
-        <v>-3.442029840268458</v>
+        <v>-3.359490711940626</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.381736539880216</v>
       </c>
       <c r="E60">
-        <v>-13.99133839587021</v>
+        <v>-9.785826097478891</v>
       </c>
       <c r="F60">
-        <v>-0.1590259793999428</v>
+        <v>0.04629482179274822</v>
       </c>
       <c r="G60">
-        <v>-3.898129480695951</v>
+        <v>-3.560560687881839</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.444241238486346</v>
       </c>
       <c r="E61">
-        <v>-13.06021621278307</v>
+        <v>-9.814876258238098</v>
       </c>
       <c r="F61">
-        <v>0.1745608871770293</v>
+        <v>0.235577601699838</v>
       </c>
       <c r="G61">
-        <v>-3.725527383004481</v>
+        <v>-2.876826301767868</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.493528437409897</v>
       </c>
       <c r="E62">
-        <v>-12.81516689880601</v>
+        <v>-9.492195314347537</v>
       </c>
       <c r="F62">
-        <v>0.1106631108272838</v>
+        <v>0.2612934393523459</v>
       </c>
       <c r="G62">
-        <v>-5.13372595844981</v>
+        <v>-3.266415581185417</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.52952686869597</v>
       </c>
       <c r="E63">
-        <v>-12.51584835232102</v>
+        <v>-9.743566378039311</v>
       </c>
       <c r="F63">
-        <v>-0.008296246786544802</v>
+        <v>0.2501734353371654</v>
       </c>
       <c r="G63">
-        <v>-4.566829309624547</v>
+        <v>-4.308180457758199</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.547888202127177</v>
       </c>
       <c r="E64">
-        <v>-12.86143884621638</v>
+        <v>-9.449120469586578</v>
       </c>
       <c r="F64">
-        <v>-0.1568125816996626</v>
+        <v>-0.4711415628963518</v>
       </c>
       <c r="G64">
-        <v>-4.531139462722467</v>
+        <v>-4.5285801099061</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.544257636095177</v>
       </c>
       <c r="E65">
-        <v>-12.63955267678855</v>
+        <v>-9.169518898930987</v>
       </c>
       <c r="F65">
-        <v>0.09661482804320698</v>
+        <v>0.009290821542291503</v>
       </c>
       <c r="G65">
-        <v>-4.807513473452936</v>
+        <v>-5.355188726382972</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.517883352791963</v>
       </c>
       <c r="E66">
-        <v>-12.00020007401561</v>
+        <v>-10.38390618814592</v>
       </c>
       <c r="F66">
-        <v>-0.3656464890476263</v>
+        <v>-0.3259784592297664</v>
       </c>
       <c r="G66">
-        <v>-4.495987736156136</v>
+        <v>-3.993088032626282</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.464254971780799</v>
       </c>
       <c r="E67">
-        <v>-11.99366548602254</v>
+        <v>-9.547193631170694</v>
       </c>
       <c r="F67">
-        <v>-0.2227398581862668</v>
+        <v>-0.02680197456508576</v>
       </c>
       <c r="G67">
-        <v>-5.44064157945559</v>
+        <v>-5.327377092445118</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.388607654947097</v>
       </c>
       <c r="E68">
-        <v>-11.6807343466705</v>
+        <v>-9.694871697034833</v>
       </c>
       <c r="F68">
-        <v>-0.3285894732833904</v>
+        <v>-0.3408617363558651</v>
       </c>
       <c r="G68">
-        <v>-5.698115754003658</v>
+        <v>-4.402417140945451</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.294527535675464</v>
       </c>
       <c r="E69">
-        <v>-10.88053034714511</v>
+        <v>-8.98601154671816</v>
       </c>
       <c r="F69">
-        <v>-0.4760264454706605</v>
+        <v>-0.2751680594768503</v>
       </c>
       <c r="G69">
-        <v>-5.998409869902479</v>
+        <v>-4.857899911719769</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.189453170926551</v>
       </c>
       <c r="E70">
-        <v>-11.5509663955067</v>
+        <v>-8.708153438555524</v>
       </c>
       <c r="F70">
-        <v>-0.6192934161522378</v>
+        <v>-0.4276249381250853</v>
       </c>
       <c r="G70">
-        <v>-5.923801454083825</v>
+        <v>-4.435977475055451</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.084995308736068</v>
       </c>
       <c r="E71">
-        <v>-11.33291131508935</v>
+        <v>-8.019585380267221</v>
       </c>
       <c r="F71">
-        <v>-0.4348706677973726</v>
+        <v>-0.7526531126963329</v>
       </c>
       <c r="G71">
-        <v>-5.538044641447708</v>
+        <v>-5.127662261007957</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.987674752130385</v>
       </c>
       <c r="E72">
-        <v>-11.79726103983587</v>
+        <v>-9.352482834262892</v>
       </c>
       <c r="F72">
-        <v>-0.6673975396002079</v>
+        <v>-0.3315136102152727</v>
       </c>
       <c r="G72">
-        <v>-5.948351553791591</v>
+        <v>-4.962938376280713</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.91150721901401</v>
       </c>
       <c r="E73">
-        <v>-11.67503299789484</v>
+        <v>-9.041793289544644</v>
       </c>
       <c r="F73">
-        <v>-0.8022135060384246</v>
+        <v>-0.6264124056118967</v>
       </c>
       <c r="G73">
-        <v>-5.515817646604028</v>
+        <v>-5.849133976277101</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.862855968328615</v>
       </c>
       <c r="E74">
-        <v>-11.90456775992163</v>
+        <v>-9.463548187775014</v>
       </c>
       <c r="F74">
-        <v>-0.5575899850525081</v>
+        <v>-0.8040160335069163</v>
       </c>
       <c r="G74">
-        <v>-5.933661524869956</v>
+        <v>-5.150079566702083</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.848901031081789</v>
       </c>
       <c r="E75">
-        <v>-12.23607017117913</v>
+        <v>-9.337529813089565</v>
       </c>
       <c r="F75">
-        <v>-0.8228696755946331</v>
+        <v>-0.2139831863712733</v>
       </c>
       <c r="G75">
-        <v>-5.317415303790645</v>
+        <v>-4.644663166236135</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.874729067412662</v>
       </c>
       <c r="E76">
-        <v>-12.62660576960062</v>
+        <v>-10.23361066430535</v>
       </c>
       <c r="F76">
-        <v>-0.6962984499164798</v>
+        <v>-0.8656357994989631</v>
       </c>
       <c r="G76">
-        <v>-5.483763393189813</v>
+        <v>-4.944468380122599</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.936619772788675</v>
       </c>
       <c r="E77">
-        <v>-13.01631718575272</v>
+        <v>-9.742669740185793</v>
       </c>
       <c r="F77">
-        <v>-0.9783442966912667</v>
+        <v>-0.5533222361932851</v>
       </c>
       <c r="G77">
-        <v>-5.58341081072859</v>
+        <v>-4.422314468481924</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.034353631865587</v>
       </c>
       <c r="E78">
-        <v>-13.29049364454712</v>
+        <v>-9.994398553324173</v>
       </c>
       <c r="F78">
-        <v>-0.9046502474360142</v>
+        <v>-0.8377902292538577</v>
       </c>
       <c r="G78">
-        <v>-4.955644220754067</v>
+        <v>-3.818933917137194</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.155986456246607</v>
       </c>
       <c r="E79">
-        <v>-12.62247580130563</v>
+        <v>-11.62196381099895</v>
       </c>
       <c r="F79">
-        <v>-0.9142120923665289</v>
+        <v>-0.6208805680960016</v>
       </c>
       <c r="G79">
-        <v>-5.04603531227365</v>
+        <v>-5.099942501273768</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.289916863804133</v>
       </c>
       <c r="E80">
-        <v>-13.90654724855059</v>
+        <v>-11.89815544072677</v>
       </c>
       <c r="F80">
-        <v>-0.7932795635992319</v>
+        <v>-0.9666891673338777</v>
       </c>
       <c r="G80">
-        <v>-4.31219011050384</v>
+        <v>-3.817637834621213</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.421659672610297</v>
       </c>
       <c r="E81">
-        <v>-13.87062286424775</v>
+        <v>-13.33420700414316</v>
       </c>
       <c r="F81">
-        <v>-1.005991887127103</v>
+        <v>-1.017912922420791</v>
       </c>
       <c r="G81">
-        <v>-4.266046291713368</v>
+        <v>-4.208185230734121</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.532200021485788</v>
       </c>
       <c r="E82">
-        <v>-14.97577883192367</v>
+        <v>-13.23737917291115</v>
       </c>
       <c r="F82">
-        <v>-1.156754754436613</v>
+        <v>-0.73009004137888</v>
       </c>
       <c r="G82">
-        <v>-4.732865682975568</v>
+        <v>-4.444360996139832</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.609947530571778</v>
       </c>
       <c r="E83">
-        <v>-15.96047286252155</v>
+        <v>-13.56759096907647</v>
       </c>
       <c r="F83">
-        <v>-1.12213396720401</v>
+        <v>-0.8042330657664498</v>
       </c>
       <c r="G83">
-        <v>-4.881449238851904</v>
+        <v>-3.535649653802535</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.639887070961758</v>
       </c>
       <c r="E84">
-        <v>-17.31067361570053</v>
+        <v>-14.99590789888776</v>
       </c>
       <c r="F84">
-        <v>-1.505986996150259</v>
+        <v>-0.7523714677793811</v>
       </c>
       <c r="G84">
-        <v>-4.666834380313303</v>
+        <v>-2.508909490750451</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.615485566110411</v>
       </c>
       <c r="E85">
-        <v>-18.64736593091462</v>
+        <v>-15.8365240004576</v>
       </c>
       <c r="F85">
-        <v>-1.161089601055463</v>
+        <v>-1.220464491385923</v>
       </c>
       <c r="G85">
-        <v>-4.389046163090713</v>
+        <v>-4.205297755761809</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.534283379667224</v>
       </c>
       <c r="E86">
-        <v>-18.77733313493476</v>
+        <v>-18.09242408364466</v>
       </c>
       <c r="F86">
-        <v>-1.090636953447365</v>
+        <v>-1.451770349637032</v>
       </c>
       <c r="G86">
-        <v>-3.926285642897547</v>
+        <v>-2.665807662058419</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.396742803620716</v>
       </c>
       <c r="E87">
-        <v>-19.89919011475097</v>
+        <v>-18.5778629118449</v>
       </c>
       <c r="F87">
-        <v>-1.296407558139776</v>
+        <v>-0.8827291608557309</v>
       </c>
       <c r="G87">
-        <v>-3.700061822481631</v>
+        <v>-3.169101112175406</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.214317163878114</v>
       </c>
       <c r="E88">
-        <v>-21.27264911043335</v>
+        <v>-20.04409222604841</v>
       </c>
       <c r="F88">
-        <v>-1.333717225961866</v>
+        <v>-0.5929513327432134</v>
       </c>
       <c r="G88">
-        <v>-3.638204233642979</v>
+        <v>-2.620808989592194</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.99717669721129</v>
       </c>
       <c r="E89">
-        <v>-22.95442020197994</v>
+        <v>-21.12193243851006</v>
       </c>
       <c r="F89">
-        <v>-1.238867501606517</v>
+        <v>-1.022487995586452</v>
       </c>
       <c r="G89">
-        <v>-3.206477506959041</v>
+        <v>-2.743753080203028</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.766766425056601</v>
       </c>
       <c r="E90">
-        <v>-23.57132968757086</v>
+        <v>-22.54097958202765</v>
       </c>
       <c r="F90">
-        <v>-1.41113727179491</v>
+        <v>-1.573991818083085</v>
       </c>
       <c r="G90">
-        <v>-3.996083787910055</v>
+        <v>-3.334537021981049</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.545703223605065</v>
       </c>
       <c r="E91">
-        <v>-25.21066897766559</v>
+        <v>-23.70590687813081</v>
       </c>
       <c r="F91">
-        <v>-1.507990816897631</v>
+        <v>-1.662075437492367</v>
       </c>
       <c r="G91">
-        <v>-3.950615900760829</v>
+        <v>-3.025285171224944</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.357819218452094</v>
       </c>
       <c r="E92">
-        <v>-27.27688034161935</v>
+        <v>-25.16287999146264</v>
       </c>
       <c r="F92">
-        <v>-1.524607038630387</v>
+        <v>-1.709454739462888</v>
       </c>
       <c r="G92">
-        <v>-3.173471699292586</v>
+        <v>-3.136085460844273</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.232830220550473</v>
       </c>
       <c r="E93">
-        <v>-29.66202986569633</v>
+        <v>-27.12072497241285</v>
       </c>
       <c r="F93">
-        <v>-1.653541596508727</v>
+        <v>-1.615752303960416</v>
       </c>
       <c r="G93">
-        <v>-3.142795558933337</v>
+        <v>-2.530043838814834</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.188336196135555</v>
       </c>
       <c r="E94">
-        <v>-31.3276139269025</v>
+        <v>-29.77163478634098</v>
       </c>
       <c r="F94">
-        <v>-1.926001575698318</v>
+        <v>-1.950554385517295</v>
       </c>
       <c r="G94">
-        <v>-3.296419071124979</v>
+        <v>-2.548120088385815</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.243072736568642</v>
       </c>
       <c r="E95">
-        <v>-32.87508180056662</v>
+        <v>-32.19218112749891</v>
       </c>
       <c r="F95">
-        <v>-1.832488007963684</v>
+        <v>-1.801493813220538</v>
       </c>
       <c r="G95">
-        <v>-3.624810287237326</v>
+        <v>-3.887754258124987</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.411517995646643</v>
       </c>
       <c r="E96">
-        <v>-35.80293949938184</v>
+        <v>-34.61425356439744</v>
       </c>
       <c r="F96">
-        <v>-1.817754665337493</v>
+        <v>-1.889620507734766</v>
       </c>
       <c r="G96">
-        <v>-3.477673750068706</v>
+        <v>-2.436788240873856</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.688052309811573</v>
       </c>
       <c r="E97">
-        <v>-38.05475489901398</v>
+        <v>-36.70252312524256</v>
       </c>
       <c r="F97">
-        <v>-2.251298141308073</v>
+        <v>-2.137863994270917</v>
       </c>
       <c r="G97">
-        <v>-3.631743508392432</v>
+        <v>-3.636242063150431</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.095796025061056</v>
       </c>
       <c r="E98">
-        <v>-40.41441137866478</v>
+        <v>-38.77779370144867</v>
       </c>
       <c r="F98">
-        <v>-1.951636233345351</v>
+        <v>-2.026488340229717</v>
       </c>
       <c r="G98">
-        <v>-3.795538807418353</v>
+        <v>-3.321323542761165</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.593729951042802</v>
       </c>
       <c r="E99">
-        <v>-43.03108366485792</v>
+        <v>-41.85968517939779</v>
       </c>
       <c r="F99">
-        <v>-1.98836273051587</v>
+        <v>-2.234954452450838</v>
       </c>
       <c r="G99">
-        <v>-3.798980808834211</v>
+        <v>-3.615360369146125</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.221006739741714</v>
       </c>
       <c r="E100">
-        <v>-44.3841781129278</v>
+        <v>-43.34251361507642</v>
       </c>
       <c r="F100">
-        <v>-2.460091458653299</v>
+        <v>-2.32003441165757</v>
       </c>
       <c r="G100">
-        <v>-4.955965780466893</v>
+        <v>-3.778246769800079</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.880474013010097</v>
       </c>
       <c r="E101">
-        <v>-46.45948944539997</v>
+        <v>-46.47088761447728</v>
       </c>
       <c r="F101">
-        <v>-2.227992852797711</v>
+        <v>-2.468593821675633</v>
       </c>
       <c r="G101">
-        <v>-5.117989219850713</v>
+        <v>-4.357736746970492</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.680929386545294</v>
       </c>
       <c r="E102">
-        <v>-49.93837072935002</v>
+        <v>-47.83205859593983</v>
       </c>
       <c r="F102">
-        <v>-2.45646403779644</v>
+        <v>-2.389618930227534</v>
       </c>
       <c r="G102">
-        <v>-4.853683542015882</v>
+        <v>-4.456947762041862</v>
       </c>
     </row>
   </sheetData>
